--- a/planilha/Restaurante_Sabor_de_Casa_Lancamentos.xlsx
+++ b/planilha/Restaurante_Sabor_de_Casa_Lancamentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/842716d967cf9b2b/Documentos/dashboard-financeiro-excel/planilha/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{C22748C2-2819-4E72-A599-AAA6FE6CEFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8EFC68E-3AF6-485F-AF6B-73C2CDB20491}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{C22748C2-2819-4E72-A599-AAA6FE6CEFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38FD3E96-A99D-4394-BFB2-52EC5D7AD4F1}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-2190" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-2190" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Lançamentos" sheetId="1" r:id="rId1"/>
@@ -800,7 +800,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="&quot;R$ &quot;#,##0"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1032,6 +1032,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -1248,7 +1256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1411,6 +1419,24 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="20" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1423,22 +1449,31 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="20" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1453,32 +1488,8 @@
     <xf numFmtId="0" fontId="30" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="35" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14870,51 +14881,51 @@
         <v>187</v>
       </c>
       <c r="B11" s="13" cm="1">
-        <f t="array" ref="B11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Janeiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="B11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Janeiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>8631.26</v>
       </c>
       <c r="C11" s="13" cm="1">
-        <f t="array" ref="C11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Fevereiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="C11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Fevereiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>8845.9100000000017</v>
       </c>
       <c r="D11" s="13" cm="1">
-        <f t="array" ref="D11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Março")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="D11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Março")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>9923.7699999999986</v>
       </c>
       <c r="E11" s="13" cm="1">
-        <f t="array" ref="E11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Abril")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="E11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Abril")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>10759.13</v>
       </c>
       <c r="F11" s="13" cm="1">
-        <f t="array" ref="F11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Maio")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="F11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Maio")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>11241.16</v>
       </c>
       <c r="G11" s="13" cm="1">
-        <f t="array" ref="G11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Junho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="G11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Junho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>11865.84</v>
       </c>
       <c r="H11" s="13" cm="1">
-        <f t="array" ref="H11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Julho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="H11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Julho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>12958.37</v>
       </c>
       <c r="I11" s="13" cm="1">
-        <f t="array" ref="I11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Agosto")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="I11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Agosto")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>12059.26</v>
       </c>
       <c r="J11" s="13" cm="1">
-        <f t="array" ref="J11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Setembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="J11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Setembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>11177.17</v>
       </c>
       <c r="K11" s="13" cm="1">
-        <f t="array" ref="K11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Outubro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="K11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Outubro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>12257.16</v>
       </c>
       <c r="L11" s="13" cm="1">
-        <f t="array" ref="L11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Novembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="L11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Novembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>13012.7</v>
       </c>
       <c r="M11" s="13" cm="1">
-        <f t="array" ref="M11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Dezembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="M11">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Dezembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Taxas/Impostos"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>14967.869999999999</v>
       </c>
       <c r="N11" s="13">
@@ -14970,7 +14981,7 @@
         <f t="shared" si="2"/>
         <v>-13012.7</v>
       </c>
-      <c r="M12" s="17">
+      <c r="M12" s="81">
         <f t="shared" si="2"/>
         <v>-14967.869999999999</v>
       </c>
@@ -15059,51 +15070,51 @@
         <v>72</v>
       </c>
       <c r="B16" s="21" cm="1">
-        <f t="array" ref="B16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Janeiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="B16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Janeiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1400.93</v>
       </c>
       <c r="C16" s="21" cm="1">
-        <f t="array" ref="C16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Fevereiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="C16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Fevereiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1464.09</v>
       </c>
       <c r="D16" s="21" cm="1">
-        <f t="array" ref="D16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Março")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="D16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Março")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1589.02</v>
       </c>
       <c r="E16" s="21" cm="1">
-        <f t="array" ref="E16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Abril")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="E16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Abril")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1783.1</v>
       </c>
       <c r="F16" s="21" cm="1">
-        <f t="array" ref="F16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Maio")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="F16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Maio")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1946.08</v>
       </c>
       <c r="G16" s="21" cm="1">
-        <f t="array" ref="G16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Junho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="G16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Junho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>2017.85</v>
       </c>
       <c r="H16" s="21" cm="1">
-        <f t="array" ref="H16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Julho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="H16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Julho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>2074.06</v>
       </c>
       <c r="I16" s="21" cm="1">
-        <f t="array" ref="I16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Agosto")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="I16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Agosto")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1985.63</v>
       </c>
       <c r="J16" s="21" cm="1">
-        <f t="array" ref="J16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Setembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="J16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Setembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1908.46</v>
       </c>
       <c r="K16" s="21" cm="1">
-        <f t="array" ref="K16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Outubro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="K16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Outubro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1948.85</v>
       </c>
       <c r="L16" s="21" cm="1">
-        <f t="array" ref="L16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Novembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="L16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Novembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>2089.27</v>
       </c>
       <c r="M16" s="21" cm="1">
-        <f t="array" ref="M16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Dezembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="M16">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Dezembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Embalagens Delivery"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>2512.29</v>
       </c>
       <c r="N16" s="13">
@@ -15111,56 +15122,56 @@
         <v>22719.629999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="20" t="s">
         <v>74</v>
       </c>
       <c r="B17" s="21" cm="1">
-        <f t="array" ref="B17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Janeiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="B17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Janeiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>499.79</v>
       </c>
       <c r="C17" s="21" cm="1">
-        <f t="array" ref="C17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Fevereiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="C17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Fevereiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>503.76</v>
       </c>
       <c r="D17" s="21" cm="1">
-        <f t="array" ref="D17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Março")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="D17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Março")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>568.85</v>
       </c>
       <c r="E17" s="21" cm="1">
-        <f t="array" ref="E17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Abril")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="E17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Abril")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>623.61</v>
       </c>
       <c r="F17" s="21" cm="1">
-        <f t="array" ref="F17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Maio")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="F17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Maio")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>637.02</v>
       </c>
       <c r="G17" s="21" cm="1">
-        <f t="array" ref="G17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Junho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="G17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Junho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>682.67</v>
       </c>
       <c r="H17" s="21" cm="1">
-        <f t="array" ref="H17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Julho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="H17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Julho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>724.69</v>
       </c>
       <c r="I17" s="21" cm="1">
-        <f t="array" ref="I17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Agosto")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="I17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Agosto")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>656.89</v>
       </c>
       <c r="J17" s="21" cm="1">
-        <f t="array" ref="J17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Setembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="J17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Setembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>657.56</v>
       </c>
       <c r="K17" s="21" cm="1">
-        <f t="array" ref="K17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Outubro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="K17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Outubro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>714.92</v>
       </c>
       <c r="L17" s="21" cm="1">
-        <f t="array" ref="L17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Novembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="L17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Novembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>755.48</v>
       </c>
       <c r="M17" s="21" cm="1">
-        <f t="array" ref="M17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Dezembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="M17">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Dezembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Produtos de Limpeza"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>867.6</v>
       </c>
       <c r="N17" s="13">
@@ -15173,51 +15184,51 @@
         <v>76</v>
       </c>
       <c r="B18" s="21" cm="1">
-        <f t="array" ref="B18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Janeiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="B18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Janeiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>314.8</v>
       </c>
       <c r="C18" s="21" cm="1">
-        <f t="array" ref="C18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Fevereiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="C18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Fevereiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>312.45999999999998</v>
       </c>
       <c r="D18" s="21" cm="1">
-        <f t="array" ref="D18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Março")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="D18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Março")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>334.65</v>
       </c>
       <c r="E18" s="21" cm="1">
-        <f t="array" ref="E18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Abril")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="E18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Abril")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>391.83</v>
       </c>
       <c r="F18" s="21" cm="1">
-        <f t="array" ref="F18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Maio")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="F18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Maio")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>407.32</v>
       </c>
       <c r="G18" s="21" cm="1">
-        <f t="array" ref="G18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Junho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="G18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Junho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>407.1</v>
       </c>
       <c r="H18" s="21" cm="1">
-        <f t="array" ref="H18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Julho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="H18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Julho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>437.85</v>
       </c>
       <c r="I18" s="21" cm="1">
-        <f t="array" ref="I18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Agosto")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="I18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Agosto")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>405.31</v>
       </c>
       <c r="J18" s="21" cm="1">
-        <f t="array" ref="J18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Setembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="J18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Setembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>377.78</v>
       </c>
       <c r="K18" s="21" cm="1">
-        <f t="array" ref="K18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Outubro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="K18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Outubro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>435.02</v>
       </c>
       <c r="L18" s="21" cm="1">
-        <f t="array" ref="L18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Novembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="L18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Novembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>437.59</v>
       </c>
       <c r="M18" s="21" cm="1">
-        <f t="array" ref="M18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Dezembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Uniformes"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="M18">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Dezembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Uniformes"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>530.52</v>
       </c>
       <c r="N18" s="13">
@@ -15230,51 +15241,51 @@
         <v>78</v>
       </c>
       <c r="B19" s="21" cm="1">
-        <f t="array" ref="B19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Janeiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="B19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Janeiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>740.3</v>
       </c>
       <c r="C19" s="21" cm="1">
-        <f t="array" ref="C19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Fevereiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="C19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Fevereiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>802.65</v>
       </c>
       <c r="D19" s="21" cm="1">
-        <f t="array" ref="D19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Março")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="D19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Março")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>865.71</v>
       </c>
       <c r="E19" s="21" cm="1">
-        <f t="array" ref="E19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Abril")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="E19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Abril")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>962.54</v>
       </c>
       <c r="F19" s="21" cm="1">
-        <f t="array" ref="F19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Maio")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="F19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Maio")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>970.46</v>
       </c>
       <c r="G19" s="21" cm="1">
-        <f t="array" ref="G19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Junho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="G19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Junho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1086.0999999999999</v>
       </c>
       <c r="H19" s="21" cm="1">
-        <f t="array" ref="H19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Julho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="H19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Julho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1069.92</v>
       </c>
       <c r="I19" s="21" cm="1">
-        <f t="array" ref="I19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Agosto")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="I19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Agosto")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1007.39</v>
       </c>
       <c r="J19" s="21" cm="1">
-        <f t="array" ref="J19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Setembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="J19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Setembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>993.73</v>
       </c>
       <c r="K19" s="21" cm="1">
-        <f t="array" ref="K19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Outubro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="K19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Outubro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1037.75</v>
       </c>
       <c r="L19" s="21" cm="1">
-        <f t="array" ref="L19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Novembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="L19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Novembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1079.77</v>
       </c>
       <c r="M19" s="21" cm="1">
-        <f t="array" ref="M19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Dezembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$D$3:$D$10000="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="M19">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Dezembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$D$3:$D$386="Manutenção Equip."),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>1310.79</v>
       </c>
       <c r="N19" s="13">
@@ -15287,51 +15298,51 @@
         <v>51</v>
       </c>
       <c r="B20" s="21" cm="1">
-        <f t="array" ref="B20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Janeiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="B20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Janeiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>26743.930000000004</v>
       </c>
       <c r="C20" s="21" cm="1">
-        <f t="array" ref="C20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Fevereiro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="C20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Fevereiro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>28000.430000000004</v>
       </c>
       <c r="D20" s="21" cm="1">
-        <f t="array" ref="D20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Março")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="D20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Março")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>30356.93</v>
       </c>
       <c r="E20" s="21" cm="1">
-        <f t="array" ref="E20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Abril")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="E20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Abril")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>33870.29</v>
       </c>
       <c r="F20" s="21" cm="1">
-        <f t="array" ref="F20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Maio")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="F20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Maio")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>35741.19</v>
       </c>
       <c r="G20" s="21" cm="1">
-        <f t="array" ref="G20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Junho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="G20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Junho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>37322.369999999995</v>
       </c>
       <c r="H20" s="21" cm="1">
-        <f t="array" ref="H20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Julho")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="H20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Julho")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>39494.92</v>
       </c>
       <c r="I20" s="21" cm="1">
-        <f t="array" ref="I20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Agosto")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="I20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Agosto")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>36411.5</v>
       </c>
       <c r="J20" s="21" cm="1">
-        <f t="array" ref="J20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Setembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="J20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Setembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>34161</v>
       </c>
       <c r="K20" s="21" cm="1">
-        <f t="array" ref="K20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Outubro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="K20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Outubro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>38593.919999999998</v>
       </c>
       <c r="L20" s="21" cm="1">
-        <f t="array" ref="L20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Novembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="L20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Novembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>39492.51</v>
       </c>
       <c r="M20" s="21" cm="1">
-        <f t="array" ref="M20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$10000="Dezembro")*('📋 Lançamentos'!$E$3:$E$10000="Despesa")*('📋 Lançamentos'!$C$3:$C$10000="Pessoal"),'📋 Lançamentos'!$I$3:$I$10000)</f>
+        <f t="array" ref="M20">SUMPRODUCT(('📋 Lançamentos'!$B$3:$B$386="Dezembro")*('📋 Lançamentos'!$E$3:$E$386="Despesa")*('📋 Lançamentos'!$C$3:$C$386="Pessoal"),'📋 Lançamentos'!$I$3:$I$386)</f>
         <v>44715.44</v>
       </c>
       <c r="N20" s="13">
@@ -15699,7 +15710,7 @@
         <v>675268.7</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
         <v>194</v>
       </c>
@@ -16434,99 +16445,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="62" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
-      <c r="M1" s="80"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
+      <c r="P1" s="63"/>
+      <c r="Q1" s="63"/>
+      <c r="R1" s="63"/>
+      <c r="S1" s="63"/>
+      <c r="T1" s="63"/>
     </row>
     <row r="2" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:20" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="58" t="s">
+      <c r="A3" s="64" t="s">
         <v>206</v>
       </c>
-      <c r="B3" s="58"/>
-      <c r="D3" s="59" t="s">
+      <c r="B3" s="64"/>
+      <c r="D3" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="E3" s="59"/>
-      <c r="G3" s="60" t="s">
+      <c r="E3" s="65"/>
+      <c r="G3" s="66" t="s">
         <v>208</v>
       </c>
-      <c r="H3" s="60"/>
-      <c r="J3" s="61" t="s">
+      <c r="H3" s="66"/>
+      <c r="J3" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="K3" s="61"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" spans="1:20" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="59"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="J4" s="61"/>
-      <c r="K4" s="61"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
     </row>
     <row r="5" spans="1:20" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62">
+      <c r="A5" s="58">
         <f>'📊 DRE Mensal'!N9</f>
         <v>1323449</v>
       </c>
-      <c r="B5" s="62"/>
-      <c r="D5" s="63">
+      <c r="B5" s="58"/>
+      <c r="D5" s="59">
         <f>'📊 DRE Mensal'!N29</f>
         <v>38244.460000000014</v>
       </c>
-      <c r="E5" s="63"/>
-      <c r="G5" s="64">
+      <c r="E5" s="59"/>
+      <c r="G5" s="60">
         <f>AVERAGE('🎯 Indicadores KPI'!B8:M8)</f>
         <v>2.3678942671779727E-2</v>
       </c>
-      <c r="H5" s="64"/>
-      <c r="J5" s="65">
+      <c r="H5" s="60"/>
+      <c r="J5" s="61">
         <f>'📊 DRE Mensal'!N21+'📊 DRE Mensal'!N28</f>
         <v>1147504.94</v>
       </c>
-      <c r="K5" s="65"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="1:20" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" spans="1:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="62"/>
-      <c r="B7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="J7" s="65"/>
-      <c r="K7" s="65"/>
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="60"/>
+      <c r="J7" s="61"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
@@ -16840,183 +16851,204 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="69" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="76"/>
+      <c r="B1" s="69"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="71" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="78"/>
+      <c r="B3" s="71"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="67"/>
-      <c r="B4" s="67"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="72"/>
     </row>
     <row r="5" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="72" t="s">
         <v>233</v>
       </c>
-      <c r="B5" s="67"/>
+      <c r="B5" s="72"/>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="72" t="s">
         <v>217</v>
       </c>
-      <c r="B6" s="67"/>
+      <c r="B6" s="72"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="75"/>
-      <c r="B7" s="75"/>
+      <c r="A7" s="73"/>
+      <c r="B7" s="73"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="B8" s="72"/>
+      <c r="B8" s="74"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="67"/>
-      <c r="B9" s="67"/>
+      <c r="A9" s="72"/>
+      <c r="B9" s="72"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="68" t="s">
         <v>219</v>
       </c>
-      <c r="B10" s="74"/>
+      <c r="B10" s="68"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="68" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="74"/>
+      <c r="B11" s="68"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="68" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="74"/>
+      <c r="B12" s="68"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="68" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="74"/>
+      <c r="B13" s="68"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="67"/>
-      <c r="B14" s="67"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="72"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
+      <c r="A15" s="74" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="72"/>
+      <c r="B15" s="74"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="67"/>
-      <c r="B16" s="67"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="72"/>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="72" t="s">
         <v>224</v>
       </c>
-      <c r="B17" s="67"/>
+      <c r="B17" s="72"/>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="72" t="s">
         <v>225</v>
       </c>
-      <c r="B18" s="67"/>
+      <c r="B18" s="72"/>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="72" t="s">
         <v>226</v>
       </c>
-      <c r="B19" s="67"/>
+      <c r="B19" s="72"/>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="72" t="s">
         <v>236</v>
       </c>
-      <c r="B20" s="67"/>
+      <c r="B20" s="72"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
+      <c r="A21" s="72"/>
+      <c r="B21" s="72"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="74" t="s">
         <v>227</v>
       </c>
-      <c r="B22" s="72"/>
+      <c r="B22" s="74"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="67"/>
-      <c r="B23" s="67"/>
+      <c r="A23" s="72"/>
+      <c r="B23" s="72"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
+      <c r="A24" s="75" t="s">
         <v>237</v>
       </c>
-      <c r="B24" s="73"/>
+      <c r="B24" s="75"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="69" t="s">
+      <c r="A25" s="78" t="s">
         <v>238</v>
       </c>
-      <c r="B25" s="69"/>
+      <c r="B25" s="78"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="70" t="s">
+      <c r="A26" s="79" t="s">
         <v>228</v>
       </c>
-      <c r="B26" s="70"/>
+      <c r="B26" s="79"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="71" t="s">
+      <c r="A27" s="80" t="s">
         <v>229</v>
       </c>
-      <c r="B27" s="71"/>
+      <c r="B27" s="80"/>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="67"/>
-      <c r="B28" s="67"/>
+      <c r="A28" s="72"/>
+      <c r="B28" s="72"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="72" t="s">
+      <c r="A29" s="74" t="s">
         <v>230</v>
       </c>
-      <c r="B29" s="72"/>
+      <c r="B29" s="74"/>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="67"/>
-      <c r="B30" s="67"/>
+      <c r="A30" s="72"/>
+      <c r="B30" s="72"/>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="76" t="s">
         <v>231</v>
       </c>
-      <c r="B31" s="66"/>
+      <c r="B31" s="76"/>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="67"/>
-      <c r="B32" s="67"/>
+      <c r="A32" s="72"/>
+      <c r="B32" s="72"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="68" t="s">
+      <c r="A33" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="B33" s="68"/>
+      <c r="B33" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
@@ -17029,27 +17061,6 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
